--- a/ig/DM-OCTOBRE-2024/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2024/ValueSet-JDV-J17-ActiviteOperationnelle-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="1021">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240927120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-27T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1590,7 +1590,7 @@
     <t>305</t>
   </si>
   <si>
-    <t>Accompagnements dans l'activité professionnelle</t>
+    <t>Accompagnements pour mener sa vie professionnelle</t>
   </si>
   <si>
     <t>306</t>
@@ -1686,7 +1686,7 @@
     <t>322</t>
   </si>
   <si>
-    <t>Prestation de restauration (dont portage de repas)</t>
+    <t>Prestation de restauration (dont portage de repas à domicile)</t>
   </si>
   <si>
     <t>323</t>
@@ -2833,12 +2833,6 @@
   </si>
   <si>
     <t>Accession à un logement individuel</t>
-  </si>
-  <si>
-    <t>534</t>
-  </si>
-  <si>
-    <t>Accompagnement infirmier pour téléconsultation médicale</t>
   </si>
   <si>
     <t>535</t>
@@ -3351,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B498"/>
+  <dimension ref="A1:B497"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -7323,23 +7317,15 @@
         <v>1018</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B497" t="s" s="2">
         <v>1020</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="s" s="2">
-        <v>1021</v>
-      </c>
-      <c r="B498" t="s" s="2">
-        <v>1022</v>
       </c>
     </row>
   </sheetData>
